--- a/assets/docs/lop5/KHDH ca khoi - Lop 5.xlsx
+++ b/assets/docs/lop5/KHDH ca khoi - Lop 5.xlsx
@@ -701,7 +701,12 @@
           <t>4+5</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV mở bản đọc mẫu bài “Cánh đồng hoa” và chiếu vài hình ảnh về làng quê, cánh đồng hoa của người Chăm trên tivi; HS nghe
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần vận dụng, GV chiếu bảng việc nên làm / không nên làm để giữ khu phố sạch đẹp trên bài tập tương tác; HS kéo thả hoặc giơ thẻ chọn</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -952,7 +957,12 @@
           <t>11+12</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV mở bài hát Con sông tuổi thơ tôi rồi bản đọc mẫu bài “Bến sông tuổi thơ” trên tivi; HS nghe, ghi lại từ ngữ tả tâm trạng nhân vật
+Năng lực số Miền 5 (Cơ bản, bậc 2): Khi tóm tắt văn bản, GV chiếu sơ đồ bố cục ba phần còn trống trên tivi; HS thảo luận nhóm chia đoạn, đặt tên cho từng phần và ghi vào phiếu</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1077,7 +1087,8 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Trước bài đọc “Tiếng hạt nảy mầm”, GV mở vài âm thanh quen thuộc cho HS đoán tên sự vật.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Tiếng hạt nảy mầm”, GV mở vài âm thanh quen thuộc cho HS đoán tên sự vật, sau đó chiếu tranh minh hoạt và đoạn thơ phóng to
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm từng khổ thơ của một vài HS rồi mở lại; cả lớp nghe và nhận xét theo tiêu chí ngắt nhịp đúng</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1213,12 @@
           <t>18+19</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Ngôi sao sân cỏ”, GV chiếu ảnh vài môn thể thao và một đoạn phim ngắn về trận bóng của thiếu nhi; HS gọi tên môn thể thao mình thích
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc phân vai của các nhóm rồi mở lại cho cả lớp nghe; HS nhận xét theo tiêu chí đọc rõ, ngắt nghỉ đúng</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1327,7 +1343,8 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ghi âm lượt đọc diễn cảm của vài.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Bộ sưu tập độc đáo”, GV chiếu tranh minh hoạ phóng to cùng vài ảnh bộ sưu tập quen thuộc như tem, vỏ sò, mô hình
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm của vài HS rồi mở lại cho cả lớp nghe; các em nhận xét theo tiêu chí chiếu sẵn là ngắt nghỉ đúng chỗ
 KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
@@ -1452,7 +1469,12 @@
           <t>25+26</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Hành tinh kì lạ”, GV chiếu vài hình ảnh các hành tinh trong hệ Mặt Trời do thầy cô chọn từ nguồn tin cậy; HS quan sát
+Năng lực số Miền 6 (Cơ bản, bậc 2): GV gõ cho công cụ trí tuệ nhân tạo vẽ thử một hành tinh theo lời tả của HS rồi chiếu lên</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1576,7 +1598,8 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Vào chủ điểm Thiên nhiên kì thú với bài thơ “Trước cổng trời”, GV chiếu ảnh vùng núi cao, thung lũng và.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào chủ điểm Thiên nhiên kì thú với bài thơ “Trước cổng trời”, GV chiếu ảnh vùng núi cao, thung lũng và rừng già do thầy cô chọn từ nguồn tin cậy
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm từng khổ thơ của một vài HS rồi mở lại; cả lớp nhận xét theo tiêu chí chiếu sẵn là ngắt nhịp thơ đúng</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1724,12 @@
           <t>32+33</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Kì diệu rừng xanh”, GV chiếu đoạn phim ngắn về rừng nguyên sinh với nấm, cây cổ thụ, muông thú
+Năng lực số Miền 5 (Cơ bản, bậc 2): Sau bài đọc, GV chiếu bảng hai cột việc làm hại rừng và việc bảo vệ rừng; HS xếp các hành động vào đúng cột</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2080,7 +2108,8 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Trước bài thơ “Mầm non”, GV chiếu một đoạn phim tua nhanh cảnh mầm cây nhú lên khi trời chuyển từ đông sang xuân.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài thơ “Mầm non”, GV chiếu một đoạn phim tua nhanh cảnh mầm cây nhú lên khi trời chuyển từ đông sang xuân
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm từng khổ thơ của vài HS rồi mở lại; cả lớp nhận xét theo tiêu chí chiếu sẵn là ngắt nhịp thơ đúng và thể hiện được…</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2363,8 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ghi âm lượt đọc diễn cảm của một vài.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Bài ca về mặt trời”, GV chiếu đoạn phim hoạt hình Thần Gió và Mặt Trời rồi dừng ở cảnh hai nhân vật thi tài
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm của một vài HS rồi mở lại cho cả lớp nghe; các em nhận xét theo tiêu chí chiếu sẵn là ngắt nghỉ đúng và giọng đọc…</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2717,12 @@
           <t>60+61</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Khi ôn về từ đa nghĩa, GV mở từ điển tiếng Việt bản điện tử và gõ một từ nhiều nghĩa như từ chân, từ mắt
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nối câu với nghĩa đúng của từ nhiều nghĩa trong câu đó; máy chấm ngay nên HS nhận ra mình còn nhầm nghĩa chuyển với từ đồng âm</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -2795,7 +2830,8 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ghi âm lượt đọc diễn cảm của vài.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Thư gửi các học sinh”, GV chiếu tranh chủ điểm và ảnh tư liệu ngày khai giảng đầu tiên của nước ta sau năm 1945 do thầy cô chọn từ nguồn…
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm của vài HS rồi mở lại cho cả lớp nghe; các em nhận xét theo tiêu chí chiếu sẵn là đọc trang trọng</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2956,12 @@
           <t>67+68</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr"/>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Tấm gương tự học”, GV chiếu tư liệu ngắn về một vài tấm gương tự học do thầy cô chọn từ nguồn tin cậy; HS đọc
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi HS lập một bảng tự học trong tuần trên máy hoặc trong vở gồm việc cần học, thời gian, kết quả tự đánh giá</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -3045,7 +3086,8 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Trước bài đọc “Trải nghiệm để sáng tạo”.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Trải nghiệm để sáng tạo”, GV chiếu vài ví dụ về sản phẩm ra đời từ quan sát thực tế như chiếc dù lấy ý tưởng từ quả bồ công anh
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm của vài HS rồi mở lại cho cả lớp nghe; các em nhận xét theo tiêu chí chiếu sẵn là đọc rõ ý</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3212,12 @@
           <t>74+75</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr"/>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Khổ luyện thành tài”, GV chiếu một vài bức tranh của danh hoạ Lê-ô-na-đô đa Vin-xi cùng bản phác thảo trứng thời ông học vẽ
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi HS lập bảng theo dõi một việc mình muốn luyện trong hai tuần gồm ngày, số lần luyện, kết quả tự nhận xét</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -3294,7 +3341,8 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ghi âm lượt đọc diễn cảm của vài.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Thế giới trong trang sách”, GV chiếu bìa và vài trang minh hoạ của những cuốn sách thiếu nhi quen thuộc
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm của vài HS rồi mở lại cho cả lớp nghe; các em nhận xét theo tiêu chí chiếu sẵn là ngắt nghỉ đúng và giọng đọc thể…</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3467,12 @@
           <t>81+82</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr"/>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Từ những câu chuyện ấu thơ”, GV chiếu tranh minh hoạ vài truyện cổ tích quen thuộc; HS kể nhanh câu chuyện mình được nghe từ bé và nói bài học…
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một trang giới thiệu câu chuyện tuổi thơ của mình: chọn tranh minh hoạ, viết ba câu tóm tắt và một câu nêu bài học</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -3544,7 +3597,8 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Trước bài giới thiệu sách “Dế Mèn phiêu lưu kí”, GV chiếu bìa sách, vài trang minh hoạ.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài giới thiệu sách “Dế Mèn phiêu lưu kí”, GV chiếu bìa sách, vài trang minh hoạ và thông tin tác giả do thầy cô chuẩn bị
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một tấm thẻ giới thiệu cuốn sách mình thích gồm tên sách, tác giả, ba câu tóm tắt và một câu mời bạn đọc</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3723,12 @@
           <t>88+89</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr"/>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc về tinh thần học tập, GV chiếu tư liệu ngắn và ảnh về nhân vật trong bài do thầy cô chọn từ nguồn tin cậy; HS đọc
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm của vài HS rồi mở lại cho cả lớp nghe; các em nhận xét theo tiêu chí chiếu sẵn là đọc rõ ý</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -3793,7 +3852,8 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ghi âm lượt đọc diễn cảm từng khổ thơ của vài.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài thơ “Tiếng đàn ba-la-lai-ca trên sông Đà”, GV cho HS nghe một đoạn nhạc đàn ba-la-lai-ca và chiếu ảnh công trình thuỷ điện Hoà Bình do thầy cô chọn từ nguồn tin…
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm từng khổ thơ của vài HS rồi mở lại; cả lớp nhận xét theo tiêu chí chiếu sẵn là ngắt nhịp thơ đúng và thể hiện được…</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3978,12 @@
           <t>95+96</t>
         </is>
       </c>
-      <c r="H85" s="4" t="inlineStr"/>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 6 (Cơ bản, bậc 2): Ở bài đọc về trí tưởng tượng, GV gõ cho công cụ trí tuệ nhân tạo tả thử một khung cảnh theo ý HS rồi chiếu kết quả
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu bài đọc phóng to và tô màu những hình ảnh so sánh, nhân hoá trong bài; HS chỉ ra chi tiết nào là quan sát thật, chi tiết nào là tưởng tượng</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -4043,7 +4108,8 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Khởi động và Luyện đọc bài “Tranh làng Hồ”, GV chiếu ảnh chụp một số bức tranh dân gian.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khởi động và Luyện đọc bài “Tranh làng Hồ”, GV chiếu ảnh chụp một số bức tranh dân gian làng Hồ như đám cưới chuột, lợn ăn cây ráy
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Đọc hiểu, GV chiếu bảng nối “Chi tiết trong bài – Bức tranh tương ứng”; HS đọc thầm, tìm câu văn tả từng bức rồi lên nối trên màn hình</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4616,8 @@
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Khởi động bài “Một ngôi chùa độc đáo”, GV chiếu ảnh một số công trình kiến trúc.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khởi động bài “Một ngôi chùa độc đáo”, GV chiếu ảnh một số công trình kiến trúc kèm chú thích tên và nơi có công trình, phóng to chi tiết mái
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Đọc hiểu, GV chiếu bảng “Chi tiết trong bài – Điều làm nên nét độc đáo”; HS đọc thầm, tìm câu văn tương ứng rồi lên điền
 KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
@@ -7847,7 +7914,9 @@
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Đọc của tiết ôn tập cuối năm, GV chiếu văn bản lên màn hình, tô sáng những từ ngữ cần nhấn giọng và mở bản đọc mẫu để HS nghe cách…
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động đọc hiểu, GV chiếu bảng chung “Chi tiết trong bài – Điều em hiểu được”; các nhóm đọc thầm, tìm chi tiết rồi lên điền
+KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8388,9 @@
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Đọc của tiết ôn tập cuối năm, GV chiếu văn bản lên màn hình, tô sáng những từ ngữ cần nhấn giọng và mở bản đọc mẫu để HS nghe cách…
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động đọc hiểu, GV chiếu bảng chung “Chi tiết trong bài – Điều em hiểu được”; các nhóm đọc thầm, tìm chi tiết rồi lên điền
+KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8888,9 @@
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Đọc của tiết ôn tập cuối năm, GV chiếu văn bản lên màn hình, tô sáng những từ ngữ cần nhấn giọng và mở bản đọc mẫu để HS nghe cách…
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động đọc hiểu, GV chiếu bảng chung “Chi tiết trong bài – Điều em hiểu được”; các nhóm đọc thầm, tìm chi tiết rồi lên điền
+KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
     </row>
@@ -8891,7 +8964,12 @@
           <t>240</t>
         </is>
       </c>
-      <c r="H209" s="4" t="inlineStr"/>
+      <c r="H209" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Đọc của tiết ôn tập cuối năm, GV chiếu văn bản lên màn hình, tô sáng những từ ngữ cần nhấn giọng và mở bản đọc mẫu để HS nghe cách…
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động đọc hiểu, GV chiếu bảng chung “Chi tiết trong bài – Điều em hiểu được”; các nhóm đọc thầm, tìm chi tiết rồi lên điền</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
@@ -10588,7 +10666,9 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video mẫu động tác chân với gậy, cho chạy chậm và dừng hình ở nhịp khuỵu gối, nhịp đưa gậy ngang vai; HS quan sát cách cầm gậy
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV quay một lượt tập của từng tổ rồi chiếu lại; HS tự chấm theo tiêu chí chiếu sẵn là đúng nhịp, đủ biên độ, gậy giữ ngang
+KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -10691,7 +10771,8 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Quay một lượt tập của từng tổ.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video mẫu động tác nhảy và động tác điều hoà với gậy, cho chạy chậm và dừng hình ở nhịp bật nhảy, nhịp hạ gậy thả lỏng
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV quay một lượt tập của từng tổ rồi chiếu lại; HS tự chấm theo tiêu chí chiếu sẵn là bật đúng nhịp, tiếp đất êm, gậy giữ ổn định
 KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
@@ -10793,7 +10874,12 @@
           <t>16</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video mẫu động tác chân với gậy, cho chạy chậm và dừng hình ở nhịp khuỵu gối, nhịp đưa gậy ngang vai; HS quan sát cách cầm gậy
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV quay một lượt tập của từng tổ rồi chiếu lại; HS tự chấm theo tiêu chí chiếu sẵn là đúng nhịp, đủ biên độ, gậy giữ ngang</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -10857,7 +10943,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video mẫu động tác toàn thân với gậy, cho chạy chậm và dừng hình ở nhịp gập thân, nhịp đưa gậy lên cao; HS quan sát trình tự phối hợp tay, thân
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV quay một lượt tập của từng tổ rồi chiếu lại; HS tự chấm theo tiêu chí chiếu sẵn là đúng trình tự, đủ biên độ, gậy giữ đúng hướng</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -10921,7 +11012,12 @@
           <t>20</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video mẫu động tác nhảy và động tác điều hoà với gậy, cho chạy chậm và dừng hình ở nhịp bật nhảy, nhịp hạ gậy thả lỏng
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV quay một lượt tập của từng tổ rồi chiếu lại; HS tự chấm theo tiêu chí chiếu sẵn là bật đúng nhịp, tiếp đất êm, gậy giữ ổn định</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -11126,7 +11222,9 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài hoàn thiện phối hợp lăn và lộn xuôi, GV chiếu trên tivi video kĩ thuật
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lại lượt tập của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi làm động tác chưa liền mạch như dừng lâu giữa hai động tác
+KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11293,9 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài hoàn thiện phối hợp lăn và lộn xuôi, GV chiếu trên tivi video kĩ thuật
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lại lượt tập của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi làm động tác chưa liền mạch như dừng lâu giữa hai động tác
+KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -11264,7 +11364,9 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức của bài “Lộn xuôi: Vận dụng rèn luyện sức khoẻ”, GV chiếu trên tivi đoạn video kĩ thuật lộn xuôi
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lại vài lượt lộn xuôi của HS bằng điện thoại rồi chiếu chậm, cả nhóm cùng chỉ ra lỗi thường gặp như chưa cuộn tròn lưng
+KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -11333,7 +11435,9 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài hoàn thiện phối hợp lăn và lộn xuôi, GV chiếu trên tivi video kĩ thuật
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lại lượt tập của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi làm động tác chưa liền mạch như dừng lâu giữa hai động tác
+KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -11402,7 +11506,8 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở phần Hình thành kiến thức bài hoàn thiện phối hợp lăn và lộn xuôi, GV chiếu trên tivi video kĩ thuật.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài hoàn thiện phối hợp lăn và lộn xuôi, GV chiếu trên tivi video kĩ thuật
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lại lượt tập của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi làm động tác chưa liền mạch như dừng lâu giữa hai động tác
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11610,7 +11715,9 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài “Leo: Phối hợp leo”, GV chiếu trên tivi video kĩ thuật leo, cho chạy chậm và dừng ở chỗ tay bám
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lại lượt leo của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi hay gặp như bám tay quá xa
+KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -11818,7 +11925,9 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài “Trèo: Phối hợp trèo”, GV chiếu trên tivi video kĩ thuật, cho chạy chậm và dừng ở chỗ tay bám
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lượt trèo của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi hay gặp như hai tay rời thang cùng lúc, mắt nhìn xuống chân
+KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -11954,7 +12063,12 @@
           <t>50</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài “Dẫn bóng di chuyển và dẫn bóng thay đổi tốc độ”, GV chiếu trên tivi video kĩ thuật
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lượt dẫn bóng của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi hay gặp như để bóng nảy quá cao khi chạy nhanh</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -12018,7 +12132,12 @@
           <t>52</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hoàn thiện dẫn bóng thay đổi tốc độ và theo đường vòng, GV chiếu trên tivi sơ đồ đường vòng nhìn từ trên xuống kèm mũi tên chỉ hướng
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lượt dẫn bóng của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi hay gặp như để bóng văng ra ngoài khi ôm vòng</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -12186,7 +12305,8 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Chiếu clip mẫu “Làm quen động tác ném rổ bằng một tay trên vai tại chỗ” và giao cho mỗi tổ một việc quan sát riêng.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài “Chuyền và bắt bóng bằng hai tay trên cao”, GV chiếu trên tivi video kĩ thuật
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lượt chuyền bóng của vài cặp rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi hay gặp như chuyền quá mạnh, tay đón bóng cứng</t>
         </is>
       </c>
     </row>
@@ -16897,7 +17017,8 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở tiết luyện tập chung, GV cho HS làm bộ bài tập tương tác có chấm tự động về đọc, viết.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết luyện tập chung, GV cho HS làm bộ bài tập tương tác có chấm tự động về đọc, viết, so sánh và làm tròn số tự nhiên
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu bài toán thực tế có bảng số liệu, tô màu dòng cần dùng theo lời HS đọc đề; các em học cách lấy đúng số liệu</t>
         </is>
       </c>
     </row>
@@ -17298,7 +17419,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết luyện tập chung, GV cho HS làm bộ câu hỏi tương tác có chấm tự động về đọc, viết, so sánh và làm tròn số thập phân
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu bảng hàng của số thập phân phóng to, bấm sáng dần từng hàng phần mười, phần trăm theo lời HS đọc số; nhờ nhìn rõ vị trí các hàng</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -17546,7 +17672,12 @@
           <t>38</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết luyện tập chung, GV cho HS làm bộ câu hỏi tương tác có chấm tự động về số thập phân và các phép tính đã học
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu bài toán thực tế có bảng số liệu, tô màu dòng và cột cần dùng theo lời HS đọc đề; các em học cách đọc bảng</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -18044,7 +18175,9 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>SGV 3 tiết; bớt 1 tiết cho kiểm tra định kì</t>
+          <t>SGV 3 tiết; bớt 1 tiết cho kiểm tra định kì
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết luyện tập chung, GV cho HS làm bộ câu hỏi tương tác có chấm tự động; sau mỗi câu các em biết ngay đúng hay sai
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu bài toán thực tế có bảng số liệu, tô màu dòng và cột cần dùng theo lời HS đọc đề; các em học cách đọc bảng</t>
         </is>
       </c>
     </row>
@@ -18559,7 +18692,8 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Thực hành bài “Luyện tập chung”, GV chiếu các hình tam giác của bài 1 lên màn hình và.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Thực hành bài “Luyện tập chung”, GV chiếu các hình tam giác của bài 1 lên màn hình và vẽ dần đường cao ứng với đáy BC, EG, IK
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần tính diện tích, chu vi, GV mở bảng tính có sẵn công thức: HS tự tính ra vở trước rồi nhập số đo vào bảng</t>
         </is>
       </c>
     </row>
@@ -19631,7 +19765,8 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Khởi động bài “Luyện tập”, GV chiếu bài toán mua tám chiếc vòng lên màn hình.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khởi động bài “Luyện tập”, GV chiếu bài toán mua tám chiếc vòng lên màn hình cùng bảng giá
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Thực hành, GV mở bảng tính có sẵn công thức: HS tính ra vở trước rồi nhập số lượng và đơn giá để máy hiện tổng tiền</t>
         </is>
       </c>
     </row>
@@ -19851,7 +19986,12 @@
           <t>113</t>
         </is>
       </c>
-      <c r="H116" s="4" t="inlineStr"/>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khởi động bài “Luyện tập chung”, GV chiếu các hình và số liệu của bài lên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Thực hành, GV mở bảng tính có sẵn công thức: HS tính ra vở trước rồi nhập số đo để đối chiếu; khi kết quả lệch nhau</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -20290,7 +20430,9 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>SGV 3 tiết; bớt 1 tiết cho kiểm tra định kì</t>
+          <t>SGV 3 tiết; bớt 1 tiết cho kiểm tra định kì
+Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khởi động bài “Luyện tập chung”, GV chiếu các hình cần quan sát lên màn hình, xoay và tô màu từng mặt để HS nhận ra hình khối
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Thực hành, GV mở bảng tính có sẵn công thức: HS tính ra vở trước rồi nhập số đo để đối chiếu; khi kết quả lệch nhau</t>
         </is>
       </c>
     </row>
@@ -20794,7 +20936,12 @@
           <t>143</t>
         </is>
       </c>
-      <c r="H146" s="4" t="inlineStr"/>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khởi động bài “Luyện tập chung”, GV chiếu các hình và số liệu của bài lên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Thực hành, GV mở bảng tính có sẵn công thức: HS tính ra vở trước rồi nhập số đo để đối chiếu; khi kết quả lệch nhau</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -21074,7 +21221,8 @@
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Khởi động bài “Luyện tập chung”, GV chiếu các hình và số liệu của bài lên màn hình, tô.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khởi động bài “Luyện tập chung”, GV chiếu các hình và số liệu của bài lên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Thực hành, GV mở bảng tính có sẵn công thức: HS tính ra vở trước rồi nhập số đo để đối chiếu; khi kết quả lệch nhau</t>
         </is>
       </c>
     </row>
@@ -22130,7 +22278,8 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở bài “Vượt qua khó khăn”, GV chiếu một hai câu chuyện có thật về tấm gương vượt khó do thầy cô.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài “Vượt qua khó khăn”, GV chiếu một hai câu chuyện có thật về tấm gương vượt khó do thầy cô chọn từ nguồn tin cậy, kèm ảnh minh hoạ; HS đọc
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV gõ lên màn hình những khó khăn HS nêu cùng cách khắc phục mà các bạn góp ý, thành bảng hai cột</t>
         </is>
       </c>
     </row>
@@ -27667,7 +27816,9 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV mở bản ghi âm bản ngữ bài hát Back to school trong bài “Starter — A. Back to school”, chiếu lời trên tivi, HS nghe hai lượt rồi hát theo
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu mẫu My goal tree trên tivi, mỗi HS nói ba mục tiêu This year I want to… rồi cả lớp thống nhất quy tắc lớp học số: giơ tay trước khi nói
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -27703,7 +27854,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trong bài “Starter — B. Last summer”, GV chiếu video các địa điểm nổi tiếng cho trò Let’s travel!, HS xem và nói tên địa điểm bằng tiếng Anh
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV cho HS chọn một ảnh kì nghỉ hè (ảnh chụp hoặc tranh trong học liệu số) chiếu trên tivi, nói hai câu I was in… / It was fun. cho cả lớp nghe</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -27737,7 +27893,12 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Với bài “Starter — C. Classroom instructions”, GV chiếu flashcard số các lệnh Open your book, Close your book, Stand up, Sit down, mỗi thẻ kèm hình minh hoạ
+Năng lực số Miền 3 (Cơ bản, bậc 2): HS đọc chant theo bản ghi âm bản ngữ chiếu trên tivi, GV dùng điện thoại ghi âm lớp đọc chant rồi mở lại để HS so với bản mẫu về trọng âm, nhịp</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -27850,7 +28011,9 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trong bài “Unit 1: All about me! — Lesson 2 (1, 2, 3)”, GV chiếu flashcard số dolphin, pink, sandwich, table tennis cho trò Bingo
+Năng lực số Miền 3 (Cơ bản, bậc 2): GV chiếu mẫu tin nhắn ngắn gửi bạn trên tivi: Hi Nam! My favourite colour is pink. My favourite food is sandwich. What about you?; HS viết một tin nhắn tương tự vào phiếu
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -27926,7 +28089,8 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở bài Unit 1 All about me, GV chiếu tranh kèm tệp ghi âm phần nghe về đất nước, môn thể thao, con vật yêu thích.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài Unit 1 All about me, GV chiếu tranh kèm tệp ghi âm phần nghe về đất nước, môn thể thao, con vật yêu thích; HS nghe lần một nắm ý chung
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt hỏi đáp theo cặp về sở thích rồi mở lại cho cả lớp nghe; HS tự đánh giá theo tiêu chí chiếu sẵn là nói đủ câu, phát âm rõ
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -28003,7 +28167,9 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 2 Our homes, GV chiếu ảnh các kiểu nhà ở như nhà phố, chung cư, nhà sàn và mở tệp ghi âm mẫu câu hỏi, câu đáp về nơi ở
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng khảo sát nhanh của lớp về kiểu nhà ở; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để GV đánh dấu vào bảng
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28079,7 +28245,8 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Mở bài tập tương tác nghe chọn tranh và ghép từ chỉ phòng.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài Unit 2 Our homes, GV chiếu ảnh các kiểu nhà ở và sơ đồ các phòng trong nhà, mở tệp ghi âm mẫu hỏi đáp về nơi ở
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe chọn tranh và ghép từ chỉ phòng với đồ vật thường có trong phòng đó; máy chấm ngay nên HS biết mình còn nhầm từ nào
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -28156,7 +28323,9 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần luyện nói bài Unit 2 Our homes, GV chiếu bảng khảo sát của lớp về kiểu nhà và phòng mà mỗi bạn thích nhất
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một trang giới thiệu ngôi nhà mơ ước: chọn hoặc vẽ hình các phòng, ghi tên phòng bằng tiếng Anh và viết hai câu giới thiệu
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28232,7 +28401,8 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Vào bài Unit 3 My foreign friends, GV chiếu bản đồ thế giới.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 3 My foreign friends, GV chiếu bản đồ thế giới và ảnh cờ một số nước kèm tệp ghi âm mẫu; HS nghe rồi chỉ đúng nước trên bản đồ
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nối tên nước với lá cờ và điền từ còn thiếu vào câu hỏi bạn đến từ đâu
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -28309,7 +28479,9 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Ở bài Unit 3 phần tả ngoại hình bạn bè, GV chiếu bộ tranh nhân vật lên màn hình; từng cặp HS hỏi đáp bằng tiếng Anh về dáng người
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe rồi chọn đúng tranh nhân vật được tả; máy chấm ngay nên HS nhận ra mình còn nhầm từ chỉ đặc điểm gần nghĩa
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28557,8 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Mở bài tập tương tác nối từ chỉ tính cách.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần kĩ năng của bài Unit 3 My foreign friends, GV mở tệp ghi âm đoạn hội thoại tả tính cách bạn bè và chiếu tranh kèm từ khoá
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nối từ chỉ tính cách với tình huống minh hoạ và điền từ còn thiếu vào câu
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -28462,7 +28635,9 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 4 Our free-time activities, GV chiếu bộ tranh hoạt động rảnh rỗi kèm tệp ghi âm mẫu; HS nghe rồi nối hoạt động với tranh
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng khảo sát hoạt động rảnh rỗi của lớp; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô đánh dấu
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28538,7 +28713,8 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ghi âm lượt hỏi đáp về hoạt động rảnh rỗi của vài cặp.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần kĩ năng của bài Unit 4 Our free-time activities, GV mở tệp ghi âm đoạn hội thoại và chiếu tranh kèm từ khoá; HS nghe lần một nắm ý chung
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một trang giới thiệu hoạt động rảnh rỗi của nhóm: chọn biểu tượng hoạt động, ghi tần suất và viết hai câu tiếng Anh
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -28577,7 +28753,9 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần luyện tập bài Unit 4 Our free-time activities, GV mở bài tập tương tác nghe chọn tranh và ghép hoạt động rảnh rỗi với tần suất
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt hỏi đáp về hoạt động rảnh rỗi của vài cặp rồi mở cho cả lớp nghe; các em nhận xét theo tiêu chí nói đủ câu, phát âm rõ
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28615,7 +28793,9 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần kĩ năng của bài Unit 3 My foreign friends, GV mở tệp ghi âm đoạn hội thoại tả tính cách bạn bè và chiếu tranh kèm từ khoá
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nối từ chỉ tính cách với tình huống minh hoạ và điền từ còn thiếu vào câu
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28691,7 +28871,8 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Vào bài Unit 5 My future job, GV chiếu bộ tranh nghề nghiệp.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 5 My future job, GV chiếu bộ tranh nghề nghiệp kèm tệp ghi âm mẫu; HS nghe rồi nối tên nghề với tranh
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng khảo sát nghề mơ ước của lớp; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô đánh dấu
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -28768,7 +28949,9 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần luyện tập bài Unit 5 My future job, GV mở bài tập tương tác nghe chọn tranh và ghép nghề với việc người làm nghề đó thường làm
+Năng lực số Miền 6 (Cơ bản, bậc 2): GV hỏi công cụ trí tuệ nhân tạo xem một nghề cần những kĩ năng gì rồi chiếu câu trả lời
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28844,7 +29027,8 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở phần kĩ năng của bài Unit 5 My future job.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 5 My future job, GV chiếu bộ tranh nghề nghiệp kèm tệp ghi âm mẫu; HS nghe rồi nối tên nghề với tranh
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng khảo sát nghề mơ ước của lớp; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô đánh dấu
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -28883,7 +29067,9 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần kĩ năng của bài Unit 5 My future job, GV mở bài tập tương tác nghe chọn tranh nghề nghiệp và điền từ còn thiếu vào câu nói về nghề mơ ước
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi HS làm một tấm thẻ nghề mơ ước gồm tên nghề bằng tiếng Anh, một hình minh hoạ và hai câu nêu lí do
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28953,7 +29139,12 @@
           <t>36</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết Review 1, GV mở bộ bài tập tương tác tổng hợp các chủ điểm đã học; sau mỗi câu máy báo đúng
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu bảng tổng hợp từ vựng và mẫu câu theo từng chủ điểm, bấm sáng dần từng nhóm; HS nhìn bảng để ôn lại có hệ thống</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -28989,7 +29180,8 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>NLS-ST (Cơ bản 2): Mỗi nhóm làm một bảng ghép nghề với nơi làm việc bằng hình.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết hoạt động mở rộng, GV mở bộ bài tập tương tác ôn từ vựng về nghề nghiệp và nơi làm việc; sau mỗi câu máy báo đúng
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một bảng ghép nghề với nơi làm việc bằng hình và từ khoá; các nhóm đổi bảng cho nhau chơi thử, ai ghép nhanh và đúng thì thắng</t>
         </is>
       </c>
     </row>
@@ -29027,7 +29219,9 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 6 Our school rooms, GV chiếu sơ đồ các tầng của trường có chú thích phòng bằng tiếng Anh kèm tệp ghi âm
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng hai cột tên phòng và tầng; từng cặp HS hỏi đáp bằng tiếng Anh xem phòng nào ở tầng nào rồi đọc để thầy cô điền
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29103,7 +29297,9 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở bài Unit 6 phần luyện tập, GV mở bài tập tương tác nghe chọn tranh và ghép câu hỏi với câu trả lời về vị trí các phòng
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt hỏi đáp chỉ đường trong trường của vài cặp rồi mở cho cả lớp nghe; các em nhận xét theo tiêu chí nói đủ câu
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29179,7 +29375,8 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở phần kĩ năng của bài Unit 6 Our school rooms, GV chiếu tranh.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần kĩ năng của bài Unit 6 Our school rooms, GV chiếu tranh kèm từ khoá và mở tệp ghi âm; HS nghe lần một nắm ý chung
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe chọn tranh và điền từ chỉ vị trí còn thiếu; máy chấm ngay nên HS nhận ra mình còn nhầm tầng, nhầm hướng
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -29256,7 +29453,9 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 7 về hoạt động yêu thích ở trường, GV chiếu bộ tranh hoạt động kèm tệp ghi âm mẫu; HS nghe rồi nối hoạt động với tranh
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng khảo sát hoạt động yêu thích của lớp; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô đánh dấu
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29332,7 +29531,8 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ở bài Unit 7 về hoạt động yêu thích.
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Ở bài Unit 7 về hoạt động yêu thích, GV mở bài hát của bài học trên màn hình cho cả lớp hát theo
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe chọn tranh và ghép câu hỏi lí do với câu trả lời; máy chấm ngay nên HS nhận ra mình còn nhầm cách dùng từ nối
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -29409,7 +29609,9 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần kĩ năng của bài Unit 7, GV chiếu tranh kèm từ khoá và mở tệp ghi âm đoạn hội thoại; HS nghe lần một nắm ý chung
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một trang giới thiệu hoạt động yêu thích ở trường: chọn hình, ghi tên hoạt động và viết hai câu nêu lí do bằng tiếng Anh
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29485,7 +29687,8 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Vào bài Unit 8 In our classroom, GV chiếu ảnh lớp học có chú thích đồ vật bằng tiếng Anh.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 8 In our classroom, GV chiếu ảnh lớp học có chú thích đồ vật bằng tiếng Anh kèm tệp ghi âm; HS nghe rồi chỉ đúng đồ vật trên ảnh
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng liệt kê đồ dùng trong lớp; từng cặp HS hỏi đáp bằng tiếng Anh xem lớp mình có gì, ở đâu rồi đọc để thầy cô điền
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -29562,7 +29765,9 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở bài Unit 8 phần hỏi vị trí đồ vật, GV mở bài tập tương tác nghe chọn tranh và kéo đồ vật về đúng vị trí theo lời mô tả
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt hỏi đáp về vị trí đồ vật của vài cặp rồi mở cho cả lớp nghe; các em nhận xét theo tiêu chí nói đủ câu
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29638,7 +29843,8 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Mở bài tập tương tác nghe.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần kĩ năng của bài Unit 8 In our classroom, GV chiếu tranh lớp học kèm từ khoá và mở tệp ghi âm; HS nghe lần một nắm ý chung
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe rồi kéo đồ vật về đúng vị trí và điền từ chỉ vị trí còn thiếu
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -29715,7 +29921,9 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 9 Our outdoor activities, GV chiếu bộ tranh hoạt động ngoài trời và tên địa điểm kèm tệp ghi âm mẫu; HS nghe rồi nối hoạt động với nơi diễn ra
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng khảo sát hoạt động ngoài trời mà lớp thích; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô đánh dấu
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29791,7 +29999,8 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Listen and repeat của Unit 9 “Our outdoor activities”, GV chiếu tranh các hoạt động ngoài trời lên màn.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Let's sing của Unit 9 “Our outdoor activities”, GV mở bài hát What did you do? kèm lời chạy trên màn hình
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động Read and write, GV chiếu đoạn văn còn chỗ trống lên màn hình; các nhóm bàn nhau rồi lên điền từ vào chỗ trống
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -29868,7 +30077,9 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần kĩ năng của bài Unit 8 In our classroom, GV chiếu tranh lớp học kèm từ khoá và mở tệp ghi âm; HS nghe lần một nắm ý chung
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe rồi kéo đồ vật về đúng vị trí và điền từ chỉ vị trí còn thiếu
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29944,7 +30155,8 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ở phần Warm-up Let's chant.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 10 “Our school trip”, GV chiếu tranh chuyến đi tham quan lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up Let's chant, GV mở bản chant có chữ chạy theo nhịp trên màn hình cho cả lớp đọc đồng thanh
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -30021,7 +30233,9 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 10 “Our school trip”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Secret boxes, GV chiếu các hộp bí mật trên màn hình; HS chọn hộp, đặt câu hỏi Did they go to…? để đoán nơi bên trong
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30097,7 +30311,8 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Listen and repeat của Unit 10 “Our school trip”, GV mở bản nghe mẫu hai từ November.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 10 “Our school trip”, GV chiếu tranh chuyến đi tham quan lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up Let's chant, GV mở bản chant có chữ chạy theo nhịp trên màn hình cho cả lớp đọc đồng thanh
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -30136,7 +30351,9 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 10 “Our school trip”, GV mở bản nghe mẫu hai từ November, December và chiếu chữ có đánh dấu trọng âm ở âm tiết thứ hai…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Whisper, sau mỗi lượt truyền tin GV chiếu câu gốc lên màn hình; hai đội đối chiếu câu mình nói với câu gốc
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30208,7 +30425,8 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở phần Warm-up trò chơi Hot seat, GV chiếu từ khoá lên màn hình cho cả lớp nhìn trừ bạn ngồi ghế nóng.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Read and match của Review 2, GV chiếu các câu và tranh lên màn hình, cho hiện lần lượt từng cặp để HS đọc và nối thử
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Hot seat, GV chiếu từ khoá lên màn hình cho cả lớp nhìn trừ bạn ngồi ghế nóng; các nhóm gợi ý bằng tiếng Anh để bạn đoán</t>
         </is>
       </c>
     </row>
@@ -30244,7 +30462,12 @@
           <t>70</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr"/>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết hoạt động mở rộng, GV mở bộ bài tập tương tác ôn từ vựng về nghề nghiệp và nơi làm việc; sau mỗi câu máy báo đúng
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một bảng ghép nghề với nơi làm việc bằng hình và từ khoá; các nhóm đổi bảng cho nhau chơi thử, ai ghép nhanh và đúng thì thắng</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -30278,7 +30501,12 @@
           <t>71</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr"/>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Read của Extension activities 2, GV chiếu đoạn đọc lên màn hình và tô sáng dần các từ khoá về chuyến đi
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Multiple choice, GV chiếu từng câu hỏi cùng bốn phương án; các nhóm chọn đáp án rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -30348,7 +30576,8 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Look, listen and repeat của Unit 11 “Family time”, GV chiếu tranh các việc gia đình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 11 “Family time”, GV chiếu tranh các việc gia đình cùng làm và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up Let's sing, GV mở bài hát có lời chạy trên màn hình cho cả lớp hát kèm động tác
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -30425,7 +30654,9 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 11 “Family time”, GV chiếu tranh lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Whisper, sau mỗi lượt truyền tin GV chiếu câu gốc lên màn hình; hai đội đối chiếu câu mình nói với câu gốc
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30501,7 +30732,8 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ở phần Warm-up.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 11 “Family time”, GV chiếu tranh lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát Did you swim last Sunday? có lời chạy trên màn hình cho cả lớp hát kèm động tác
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -30578,7 +30810,9 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần mở đầu Unit 12 “Our Tet holiday”, GV chiếu bức tranh chủ đề phóng to lên màn hình, cho hiện dần từng chi tiết như bánh chưng, hoa đào
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Việc gia đình làm ngày Tết – Câu nói bằng tiếng Anh”; các cặp hỏi đáp rồi lên điền câu của mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30654,7 +30888,8 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Look, listen and repeat của Unit 12 “Our Tet holiday”, GV chiếu tranh các việc chuẩn bị Tết và.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 12 “Our Tet holiday”, GV chiếu tranh các việc chuẩn bị Tết và mở bản nghe mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Missing letters, GV chiếu các cụm từ về ngày Tết bị khuyết chữ cái; các nhóm điền chữ còn thiếu trên màn hình rồi bấm kiểm tra
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -30731,7 +30966,9 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Warm-up của Unit 12 “Our Tet holiday”, GV chiếu đoạn phim ngắn về Tết ở các vùng miền lấy từ nguồn tin cậy
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Vùng miền – Hoạt động ngày Tết”; các nhóm lên điền điều xem được từ đoạn phim và điều mình biết
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30807,7 +31044,8 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ở phần Warm-up Let's chant.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 13 “Our special days”, GV chiếu tranh các ngày lễ và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up Let's chant, GV mở bản chant có chữ chạy theo nhịp trên màn hình cho cả lớp đọc đồng thanh
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -30884,7 +31122,9 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 12 “Our Tet holiday”, GV chiếu tranh các việc chuẩn bị Tết và mở bản nghe mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Missing letters, GV chiếu các cụm từ về ngày Tết bị khuyết chữ cái; các nhóm điền chữ còn thiếu trên màn hình rồi bấm kiểm tra
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30960,7 +31200,8 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Listen and tick của Unit 13 “Our special days”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 13 “Our special days”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi đoán món ăn, đồ uống, GV chiếu lần lượt ảnh bị che một phần; ba đội đoán tên bằng tiếng Anh
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31037,7 +31278,9 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Warm-up của Unit 14 “Staying healthy”, GV chiếu bộ ảnh món ăn lên màn hình và cho HS phân loại đồ ăn có lợi và ít có lợi cho sức khoẻ
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Món ăn – Có lợi hay ít có lợi – Vì sao”; các nhóm lên điền rồi đọc bảng của nhau
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31113,7 +31356,8 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở phần Warm-up trò chơi Look and choose, GV chiếu tranh.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 14 “Staying healthy”, GV chiếu tranh lên màn hình và mở bản nghe mẫu lời khuyên giữ sức khoẻ
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Look and choose, GV chiếu tranh cùng ba phương án từ vựng; các nhóm chọn phương án đúng rồi bấm kiểm tra
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31190,7 +31434,9 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and number của Unit 14 “Staying healthy”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh số
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát Staying healthy có lời chạy trên màn hình cho cả lớp hát, sau đó chia hai nhóm hát nối tiếp theo phần lời đang sáng và nghe…
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31266,7 +31512,8 @@
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Look, listen and repeat của Unit 15 “Our health”, GV chiếu tranh các biểu hiện sức khoẻ.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 15 “Our health”, GV chiếu tranh các biểu hiện sức khoẻ và mở bản nghe mẫu
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Warm-up trình bày dự án, các nhóm chiếu bài giới thiệu lối sống lành mạnh của mình lên màn hình bằng vài trang trình chiếu đơn giản
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31343,7 +31590,9 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 15 “Our health”, GV chiếu tranh lên màn hình và mở bản nghe mẫu mẫu câu What's the matter?
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Warm-up, GV chiếu lời bài hát What's the matter? còn khuyết từ trên màn hình; các nhóm bàn nhau điền từ còn thiếu rồi cùng hát lại cả bài theo lời vừa…
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31419,7 +31668,8 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ở hoạt động Conversation making, GV chiếu khung hội thoại mẫu lên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Warm-up của Unit 15 “Our health”, GV chiếu bảng từ vựng về sức khoẻ và lời khuyên lên màn hình để HS tra lại khi quên từ
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động Conversation making, GV chiếu khung hội thoại mẫu lên màn hình; các cặp dựng đoạn hội thoại của mình theo khung rồi trình bày
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31494,7 +31744,12 @@
           <t>103</t>
         </is>
       </c>
-      <c r="H106" s="4" t="inlineStr"/>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Listen and tick của Review 3, GV chiếu tranh lên màn hình và mở bản nghe các tình huống từ Unit 11 đến Unit 15
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Colourful butterflies, GV chiếu bảng nhiều chủ đề lên màn hình; các nhóm chọn đúng chủ đề mình muốn ôn rồi lấy mẫu câu tương ứng</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -31528,7 +31783,12 @@
           <t>104</t>
         </is>
       </c>
-      <c r="H107" s="4" t="inlineStr"/>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Warm-up của Review 3, GV mở bài hát Staying healthy có lời chạy trên màn hình; sau khi hát
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Fun time, GV mở bài tập tương tác nối câu hỏi với câu trả lời của các đơn vị đã học; HS chọn rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -31598,7 +31858,8 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Look, listen and repeat của Unit 16 “Seasons and the weather”, GV chiếu tranh bốn mùa.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 16 “Seasons and the weather”, GV chiếu tranh bốn mùa và mở bản nghe mẫu
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Warm-up trình bày dự án, các nhóm chiếu bài khảo sát về vấn đề sức khoẻ và lời khuyên lên màn hình bằng vài trang trình chiếu đơn giản
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31675,7 +31936,9 @@
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Warm-up của Unit 15 “Our health”, GV chiếu bảng từ vựng về sức khoẻ và lời khuyên lên màn hình để HS tra lại khi quên từ
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động Conversation making, GV chiếu khung hội thoại mẫu lên màn hình; các cặp dựng đoạn hội thoại của mình theo khung rồi trình bày
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31751,7 +32014,8 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở phần Warm-up trò chơi Matching pairs, GV chiếu các thẻ mùa.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 16 “Seasons and the weather”, GV chiếu tranh bốn mùa cùng trang phục tương ứng lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Matching pairs, GV chiếu các thẻ mùa và thẻ trang phục úp xuống; các nhóm lật tìm cặp phù hợp
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31828,7 +32092,9 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 16 “Seasons and the weather”, GV chiếu tranh bốn mùa và mở bản nghe mẫu
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Warm-up trình bày dự án, các nhóm chiếu bài khảo sát về vấn đề sức khoẻ và lời khuyên lên màn hình bằng vài trang trình chiếu đơn giản
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31904,7 +32170,8 @@
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Look, listen and repeat của Unit 17 “Stories for children”.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 17 “Stories for children”, GV chiếu tranh các nhân vật chính trong truyện và mở bản nghe mẫu mẫu câu Who are the main characters…?
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Car Racing, GV chiếu câu hỏi về nhân vật chính lên màn hình; các nhóm trả lời để xe tiến lên
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31981,7 +32248,9 @@
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 16 “Seasons and the weather”, GV chiếu tranh bốn mùa cùng trang phục tương ứng lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Matching pairs, GV chiếu các thẻ mùa và thẻ trang phục úp xuống; các nhóm lật tìm cặp phù hợp
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -32057,7 +32326,8 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nơi đến – Phương tiện – Vì sao chọn”.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 18 “Means of transport”, GV chiếu ảnh một số danh thắng Việt Nam kèm tên nơi chốn và phương tiện đến đó
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nơi đến – Phương tiện – Vì sao chọn”; các cặp hỏi đáp rồi lên điền
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -32134,7 +32404,9 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 17 “Stories for children”, GV chiếu tranh các nhân vật chính trong truyện và mở bản nghe mẫu mẫu câu Who are the main characters…?
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Car Racing, GV chiếu câu hỏi về nhân vật chính lên màn hình; các nhóm trả lời để xe tiến lên
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -32172,7 +32444,9 @@
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 18, GV chiếu tranh phương tiện lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Slow motion, GV chiếu ảnh danh thắng hiện ra thật chậm; các nhóm đoán tên nơi chốn bằng tiếng Anh
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -32287,7 +32561,9 @@
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 18 “Means of transport”, GV chiếu tranh phương tiện lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát Where do you want to visit? có lời chạy trên màn hình cho cả lớp hát
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -32363,7 +32639,8 @@
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ở phần Warm-up, GV mở bài hát What do you think of…? có lời chạy trên màn hình cho cả lớp hát.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 19 “Places of interest”, GV chiếu ảnh các địa danh lên màn hình và mở bản nghe mẫu mẫu câu What do you think of…?
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát What do you think of…? có lời chạy trên màn hình cho cả lớp hát
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -32440,7 +32717,9 @@
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 19, GV chiếu tranh địa danh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Địa danh – Cảm nghĩ của em – Vì sao”; các cặp hỏi đáp rồi lên điền
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -32516,7 +32795,8 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Look, listen and repeat của Unit 20 “Our summer holidays”, GV chiếu tranh các nơi.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 20 “Our summer holidays”, GV chiếu tranh các nơi có thể đi nghỉ hè kèm tên gọi và mở bản nghe mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi đoán nơi chốn, GV chiếu ảnh bị che một phần; các nhóm đoán tên bằng tiếng Anh rồi bấm chọn
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -32593,7 +32873,9 @@
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 19 “Places of interest”, GV chiếu ảnh các địa danh lên màn hình và mở bản nghe mẫu mẫu câu What do you think of…?
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát What do you think of…? có lời chạy trên màn hình cho cả lớp hát
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -32669,7 +32951,8 @@
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở phần Warm-up, GV chiếu các câu hỏi đã học lên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 20 “Our summer holidays”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up, GV chiếu các câu hỏi đã học lên màn hình; hai đội thi trả lời nhanh, sau mỗi lượt máy hiện đáp án và số câu đúng để các nhóm biết…
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -32744,7 +33027,12 @@
           <t>136</t>
         </is>
       </c>
-      <c r="H139" s="4" t="inlineStr"/>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Listen and tick của Review 4, GV chiếu tranh lên màn hình và mở bản nghe các tình huống từ Unit 16 đến Unit 20
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát Where are you going to go this summer? có lời chạy trên màn hình cho cả lớp hát</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -32780,7 +33068,8 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở phần Review 4, GV chiếu lần lượt các mẫu câu đã học trong năm lên màn hình cho HS đọc lại theo nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Review 4, GV chiếu lần lượt các mẫu câu đã học trong năm lên màn hình cho HS đọc lại theo nhóm
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Racing game, GV chiếu câu hỏi lên màn hình; các nhóm trả lời để xe tiến lên</t>
         </is>
       </c>
     </row>
@@ -35458,7 +35747,9 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 3 (Cơ bản, bậc 2): Ở tiết nhạc cụ và Vận dụng – Sáng tạo tổng kết chủ đề “Khúc ca ngày mới”, HS luyện mẫu tiết tấu đệm cho bài Chim sơn ca
+Năng lực số Miền 2 (Cơ bản, bậc 2): Cả lớp nghe lại bản quay và nhận xét theo tiêu chí chiếu sẵn: gõ đúng mẫu tiết tấu, đều phách, hoà với giọng hát
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -35525,7 +35816,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): HS nghe bản thu bài Lí đất giồng từ học liệu số, nhìn lời và mẫu gõ đệm trên màn hình để ôn đúng nhịp trước khi tập với nhạc cụ.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -35591,7 +35886,9 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở tiết tổng kết chủ đề “Giai điệu quê hương”, GV mở bản thu bài Lí đất giồng cùng một vài điệu lí khác của Nam Bộ; HS nghe
+Năng lực số Miền 3 (Cơ bản, bậc 2): Các nhóm dàn dựng tiết mục hát kết hợp gõ đệm và vận động; GV quay lại rồi chiếu chậm đoạn gõ đệm để mỗi nhóm nhìn thấy tay mình vào phách sớm hay…
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -35727,7 +36024,9 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở tiết tổng kết chủ đề “Bay vào tương lai”, GV mở bản thu các bài đã học và chiếu mẫu tiết tấu nhịp hai bốn phóng to; HS nghe
+Năng lực số Miền 3 (Cơ bản, bậc 2): Các nhóm dàn dựng tiết mục hát kết hợp gõ đệm; GV quay lại rồi chiếu chậm đoạn gõ để mỗi nhóm nhìn thấy tay mình vào phách sớm hay muộn
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -35793,7 +36092,11 @@
           <t>14</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): HS xem video mẫu thể hiện tiết tấu và giai điệu bằng nhạc cụ trên màn hình, nhận ra chỗ mình gõ chưa đúng rồi tập lại theo mẫu.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -35859,7 +36162,9 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần tổng kết chủ đề “Chào mùa xuân đến”, GV mở bản thu Xô-nát Ánh trăng từ học liệu số, chiếu kèm vài dòng giới thiệu về tác phẩm
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay tiết mục tổng hợp hát – đệm nhạc cụ – vận động của từng nhóm rồi chiếu lên tivi
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -36060,8 +36365,9 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>QPAN: Cho HS nghe/hát bài hát về biển, đảo quê hương; qua đó giới thiệu chủ quyền, quyền chủ quyền biển, đảo Việt Nam và gương dũng cảm cứu hộ, cứu nạn của cán bộ, chiến sĩ.
-KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Khám phá tổng kết chủ đề “Thiên nhiên tươi đẹp”, GV chiếu mẫu tiết tấu nhịp ba bốn lên màn hình và mở bản đệm mẫu cho bài Em đi giữa biển…
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Vận dụng – Sáng tạo, GV ghi âm phần hoà tấu của từng nhóm rồi mở lại cho cả lớp nghe
+QPAN: Cho HS nghe/hát bài hát về biển, đảo quê hương; qua đó giới thiệu chủ quyền, quyền chủ quyền biển, đảo Việt Nam và gương dũng cảm cứu hộ, cứu nạn của cán bộ, chiến sĩ.</t>
         </is>
       </c>
     </row>
@@ -36127,7 +36433,11 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 3 (Cơ bản, bậc 2): HS được GV ghi hình phần gõ đệm bài Tuổi hồng ơi của nhóm, xem lại trên tivi để chỉnh chỗ chưa khớp nhịp trước khi biểu diễn.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -36193,7 +36503,9 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Khởi động tổng kết chủ đề “Ước mơ tuổi thơ”, GV mở bản thu bài Tuổi hồng ơi từ học liệu số và chiếu lời lên màn hình
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Vận dụng – Sáng tạo, GV quay tiết mục tổng hợp của từng nhóm rồi chiếu lên tivi; các nhóm tự xem lại để chỉnh chỗ vào nhạc chưa khớp
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -36331,7 +36643,9 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Khởi động tổng kết chủ đề “Âm nhạc nước ngoài”, GV mở bản thu bài Đất nước tươi đẹp sao từ học liệu số và chiếu lời cùng tên nước lên màn…
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Vận dụng – Sáng tạo, GV quay tiết mục của từng nhóm rồi chiếu lên tivi; các nhóm tự xem lại để chỉnh chỗ vào nhạc chưa khớp
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -36433,7 +36747,9 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Khởi động tổng kết chủ đề “Khúc ca hè về”, GV mở bản thu bài hát từ học liệu số và chiếu lời lên màn hình
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Vận dụng – Sáng tạo, GV quay tiết mục của từng nhóm rồi chiếu lên tivi; các nhóm tự xem lại để chỉnh chỗ vào nhạc chưa khớp
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>

--- a/assets/docs/lop5/KHDH ca khoi - Lop 5.xlsx
+++ b/assets/docs/lop5/KHDH ca khoi - Lop 5.xlsx
@@ -2611,11 +2611,7 @@
           <t>57</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 2): Khi ôn về từ đa nghĩa.</t>
-        </is>
-      </c>
+      <c r="H52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -8926,11 +8922,7 @@
           <t>239</t>
         </is>
       </c>
-      <c r="H208" s="4" t="inlineStr">
-        <is>
-          <t>NLS-GT (Cơ bản 2): Ở hoạt động đọc hiểu, GV chiếu bảng chung “Chi tiết trong bài – Điều em hiểu được”.</t>
-        </is>
-      </c>
+      <c r="H208" s="4" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
@@ -10355,7 +10347,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS đọc được sơ đồ đường di chuyển của “Bài tập phối hợp biến đổi đội hình” và dự đoán đúng vị trí tổ mình.
+          <t>Năng lực số 1.1 CB2c: HS đọc được sơ đồ đường di chuyển của “Bài tập phối hợp đội hình đội ngũ” và dự đoán đúng vị trí tổ mình.
 KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
@@ -10424,8 +10416,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS đọc được sơ đồ đường di chuyển của “Bài tập phối hợp biến đổi đội hình” và dự đoán đúng vị trí tổ mình.
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -10562,8 +10553,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.5 CB2a: HS xin phép bạn trước khi chiếu clip và tự xoá clip sau tiết học.
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -10631,8 +10621,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Động tác vươn thở, động tác tay với gậy” với động tác mẫu trong clip.
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -10666,9 +10655,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video mẫu động tác chân với gậy, cho chạy chậm và dừng hình ở nhịp khuỵu gối, nhịp đưa gậy ngang vai; HS quan sát cách cầm gậy
-Năng lực số Miền 5 (Cơ bản, bậc 2): GV quay một lượt tập của từng tổ rồi chiếu lại; HS tự chấm theo tiêu chí chiếu sẵn là đúng nhịp, đủ biên độ, gậy giữ ngang
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -10771,9 +10758,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video mẫu động tác nhảy và động tác điều hoà với gậy, cho chạy chậm và dừng hình ở nhịp bật nhảy, nhịp hạ gậy thả lỏng
-Năng lực số Miền 5 (Cơ bản, bậc 2): GV quay một lượt tập của từng tổ rồi chiếu lại; HS tự chấm theo tiêu chí chiếu sẵn là bật đúng nhịp, tiếp đất êm, gậy giữ ổn định
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -10807,8 +10792,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.2 CB2a: HS quay và xem chậm được clip mình thực hiện “Hoàn thiện bài thể dục với gậy”, tự chỉ ra lỗi của mình và của bạn.
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -10978,11 +10962,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Động tác lăn” với động tác mẫu trong clip.</t>
-        </is>
-      </c>
+      <c r="H22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -11049,7 +11029,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.2 CB2a: HS quay và xem chậm được clip mình thực hiện “Hoàn thiện bài thể dục với gậy”, tự chỉ ra lỗi của mình và của bạn.</t>
+          <t>Năng lực số 3.2 CB2a: HS quay và xem chậm được clip mình thực hiện “Động tác nhảy, động tác điều hoà với gậy”, tự chỉ ra lỗi của mình và của bạn.</t>
         </is>
       </c>
     </row>
@@ -11081,11 +11061,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS điền và đọc được bảng theo dõi phần đội hình đội ngũ, tự xác định nội dung cần cố gắng thêm.</t>
-        </is>
-      </c>
+      <c r="H25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -11117,7 +11093,7 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Động tác lăn” với động tác mẫu trong clip.
+          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Bài tập rèn luyện kĩ năng lăn” với động tác mẫu trong clip.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11152,8 +11128,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được nhật kí vận động gắn với động tác lăn và tự điều chỉnh kế hoạch sau một tuần.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -11187,7 +11162,8 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được nhật kí vận động gắn với các kĩ năng lăn, lộn xuôi, leo, trèo đã học và tự điều chỉnh kế hoạch sau một tuần.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video mẫu bài phối hợp lăn, cho chạy chậm và dừng hình ở tư thế thu người, ở lúc tay chống hỗ trợ
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV quay một lượt tập của từng tổ rồi chiếu lại; HS tự chấm theo tiêu chí chiếu sẵn là thu người gọn, lăn thẳng hướng, kết thúc giữ thăng bằng
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11222,8 +11198,8 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài hoàn thiện phối hợp lăn và lộn xuôi, GV chiếu trên tivi video kĩ thuật
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lại lượt tập của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi làm động tác chưa liền mạch như dừng lâu giữa hai động tác
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết trò chơi và bài tập bổ trợ lăn, GV chiếu sơ đồ khu tập và luật chơi lên màn hình rồi cùng HS bàn cách chia lượt sao cho ai cũng được…
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video các bài tập bổ trợ, dừng hình ở tư thế chuẩn bị và tư thế kết thúc; HS đối chiếu với động tác lăn đã học ở tiết trước để hiểu…
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11258,7 +11234,7 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được nhật kí vận động gắn với các kĩ năng lăn, lộn xuôi, leo, trèo đã học và tự điều chỉnh kế hoạch sau một tuần.
+          <t>Năng lực số 3.2 CB2a: HS quay và xem chậm được clip mình thực hiện “Bài tập rèn luyện kĩ năng lăn”, tự chỉ ra lỗi của mình và của bạn.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11293,8 +11269,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài hoàn thiện phối hợp lăn và lộn xuôi, GV chiếu trên tivi video kĩ thuật
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lại lượt tập của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi làm động tác chưa liền mạch như dừng lâu giữa hai động tác
+          <t>Năng lực số 5.2 CB2b: HS lập được nhật kí vận động gắn với động tác lăn và tự điều chỉnh kế hoạch sau một tuần.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11329,7 +11304,7 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Động tác lộn xuôi” với động tác mẫu trong clip.
+          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Bài tập rèn luyện kĩ năng lộn xuôi” với động tác mẫu trong clip.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11364,154 +11339,153 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề 3: Tư thế và kĩ năng vận động cơ bản</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề 3: Tư thế và kĩ năng vận động cơ bản — Bài 2: Bài tập rèn luyện kĩ năng lộn xuôi (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>6 tiết</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video mẫu bài phối hợp lộn xuôi, cho chạy chậm và dừng hình ở tư thế chống tay, thu cằm, đẩy hông
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV quay một lượt tập của từng tổ rồi chiếu lại; HS tự chấm theo tiêu chí chiếu sẵn là chống tay đúng chỗ, thu cằm, lộn thẳng hướng
+KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề 3: Tư thế và kĩ năng vận động cơ bản</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề 3: Tư thế và kĩ năng vận động cơ bản — Bài 2: Bài tập rèn luyện kĩ năng lộn xuôi (Tiết 4)</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>6 tiết</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết trò chơi và bài tập bổ trợ lộn xuôi, GV chiếu sơ đồ khu tập và luật chơi lên màn hình rồi cùng HS bàn cách chia lượt để ai cũng được…
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video các bài tập bổ trợ, dừng hình ở tư thế chuẩn bị và tư thế kết thúc; HS đối chiếu với động tác lộn xuôi đã học để hiểu bài tập…
+KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề 3: Tư thế và kĩ năng vận động cơ bản</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề 3: Tư thế và kĩ năng vận động cơ bản — Bài 2: Bài tập rèn luyện kĩ năng lộn xuôi (Tiết 5)</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>6 tiết</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 3.2 CB2a: HS quay và xem chậm được clip mình thực hiện “Bài tập rèn luyện kĩ năng lộn xuôi”, tự chỉ ra lỗi của mình và của bạn.
+KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề 3: Tư thế và kĩ năng vận động cơ bản</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề 3: Tư thế và kĩ năng vận động cơ bản — Bài 2: Bài tập rèn luyện kĩ năng lộn xuôi (Tiết 6)</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>6 tiết</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
           <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức của bài “Lộn xuôi: Vận dụng rèn luyện sức khoẻ”, GV chiếu trên tivi đoạn video kĩ thuật lộn xuôi
 Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lại vài lượt lộn xuôi của HS bằng điện thoại rồi chiếu chậm, cả nhóm cùng chỉ ra lỗi thường gặp như chưa cuộn tròn lưng
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề 3: Tư thế và kĩ năng vận động cơ bản</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr"/>
-      <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề 3: Tư thế và kĩ năng vận động cơ bản — Bài 2: Bài tập rèn luyện kĩ năng lộn xuôi (Tiết 3)</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>6 tiết</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được nhật kí vận động gắn với các kĩ năng lăn, lộn xuôi, leo, trèo đã học và tự điều chỉnh kế hoạch sau một tuần.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề 3: Tư thế và kĩ năng vận động cơ bản</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr"/>
-      <c r="D35" s="4" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề 3: Tư thế và kĩ năng vận động cơ bản — Bài 2: Bài tập rèn luyện kĩ năng lộn xuôi (Tiết 4)</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>6 tiết</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài hoàn thiện phối hợp lăn và lộn xuôi, GV chiếu trên tivi video kĩ thuật
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lại lượt tập của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi làm động tác chưa liền mạch như dừng lâu giữa hai động tác
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề 3: Tư thế và kĩ năng vận động cơ bản</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr"/>
-      <c r="D36" s="4" t="inlineStr"/>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề 3: Tư thế và kĩ năng vận động cơ bản — Bài 2: Bài tập rèn luyện kĩ năng lộn xuôi (Tiết 5)</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>6 tiết</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được nhật kí vận động gắn với các kĩ năng lăn, lộn xuôi, leo, trèo đã học và tự điều chỉnh kế hoạch sau một tuần.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề 3: Tư thế và kĩ năng vận động cơ bản</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr"/>
-      <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề 3: Tư thế và kĩ năng vận động cơ bản — Bài 2: Bài tập rèn luyện kĩ năng lộn xuôi (Tiết 6)</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>6 tiết</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài hoàn thiện phối hợp lăn và lộn xuôi, GV chiếu trên tivi video kĩ thuật
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lại lượt tập của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi làm động tác chưa liền mạch như dừng lâu giữa hai động tác
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
@@ -11540,11 +11514,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS điền và đọc được bảng theo dõi phần hệ thống nội dung đã học, tự xác định nội dung cần cố gắng thêm.</t>
-        </is>
-      </c>
+      <c r="H38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -11611,7 +11581,7 @@
       <c r="H40" s="4" t="inlineStr">
         <is>
           <t>Điều chỉnh: Bài 2 (Tiết 6) chuyển sang tuần 19.
-Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Động tác leo” với động tác mẫu trong clip.
+Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Bài tập rèn luyện kĩ năng leo” với động tác mẫu trong clip.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11680,7 +11650,8 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được nhật kí vận động gắn với các kĩ năng lăn, lộn xuôi, leo, trèo đã học và tự điều chỉnh kế hoạch sau một tuần.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài “Leo: Phối hợp leo”, GV chiếu trên tivi video kĩ thuật leo, cho chạy chậm và dừng ở chỗ tay bám
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lại lượt leo của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi hay gặp như bám tay quá xa
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11715,8 +11686,8 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài “Leo: Phối hợp leo”, GV chiếu trên tivi video kĩ thuật leo, cho chạy chậm và dừng ở chỗ tay bám
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lại lượt leo của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi hay gặp như bám tay quá xa
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần bài tập bổ trợ leo, GV chiếu trên tivi sơ đồ sân chơi nhìn từ trên xuống kèm mũi tên chỉ đường di chuyển của từng đội
+Năng lực số Miền 5 (Cơ bản, bậc 2): Sau mỗi lượt chơi, GV chiếu bảng kết quả các đội lên tivi kèm số lần phạm luật; các nhóm nhìn bảng để tìm ra mình mất thời gian ở khâu nào và bàn…
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11751,7 +11722,7 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được nhật kí vận động gắn với các kĩ năng lăn, lộn xuôi, leo, trèo đã học và tự điều chỉnh kế hoạch sau một tuần.
+          <t>Năng lực số 3.2 CB2a: HS quay và xem chậm được clip mình thực hiện “Bài tập rèn luyện kĩ năng leo”, tự chỉ ra lỗi của mình và của bạn.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11786,7 +11757,8 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.2 CB2a: HS quay và xem chậm được clip mình thực hiện “Hoàn thiện động tác leo”, tự chỉ ra lỗi của mình và của bạn.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Vận dụng bài “Leo: Vận dụng rèn luyện sức khoẻ”, GV chiếu trên tivi video bài tập bổ trợ, cho chạy chậm ở chỗ giữ thân người sát thang và đổi tay
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lượt tập của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi làm mất sức như bám quá chặt, leo quá nhanh rồi tụt lại
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11821,7 +11793,7 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Động tác trèo” với động tác mẫu trong clip.
+          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Bài tập rèn luyện kĩ năng trèo” với động tác mẫu trong clip.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11890,7 +11862,8 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được nhật kí vận động gắn với các kĩ năng lăn, lộn xuôi, leo, trèo đã học và tự điều chỉnh kế hoạch sau một tuần.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài “Trèo: Phối hợp trèo”, GV chiếu trên tivi video kĩ thuật, cho chạy chậm và dừng ở chỗ tay bám
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lượt trèo của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi hay gặp như hai tay rời thang cùng lúc, mắt nhìn xuống chân
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11925,8 +11898,8 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài “Trèo: Phối hợp trèo”, GV chiếu trên tivi video kĩ thuật, cho chạy chậm và dừng ở chỗ tay bám
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lượt trèo của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi hay gặp như hai tay rời thang cùng lúc, mắt nhìn xuống chân
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần bài tập bổ trợ trèo, GV chiếu trên tivi sơ đồ vị trí các nhóm và thứ tự lượt tập kèm mũi tên chỉ hướng di chuyển
+Năng lực số Miền 5 (Cơ bản, bậc 2): Sau mỗi lượt, GV chiếu bảng kết quả các nhóm kèm số lần phải dừng giữa chừng; các nhóm nhìn bảng tìm ra mình mất sức ở đoạn nào rồi bàn cách chia lượt…
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11961,7 +11934,7 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được nhật kí vận động gắn với các kĩ năng lăn, lộn xuôi, leo, trèo đã học và tự điều chỉnh kế hoạch sau một tuần.
+          <t>Năng lực số 3.2 CB2a: HS quay và xem chậm được clip mình thực hiện “Bài tập rèn luyện kĩ năng trèo”, tự chỉ ra lỗi của mình và của bạn.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11996,7 +11969,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.2 CB2a: HS quay và xem chậm được clip mình thực hiện “Hoàn thiện động tác trèo”, tự chỉ ra lỗi của mình và của bạn.
+          <t>Năng lực số 5.2 CB2b: HS tự đo được nhịp tim trước và sau khi tập “Bài tập rèn luyện kĩ năng trèo”, đọc và so sánh với số máy đo.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -12031,7 +12004,7 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Làm quen với bóng rổ và tư thế dẫn bóng tại chỗ” với động tác mẫu trong clip.</t>
+          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Dẫn bóng thay đổi tốc độ, dẫn bóng theo đường vòng” với động tác mẫu trong clip.</t>
         </is>
       </c>
     </row>
@@ -12100,7 +12073,7 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS đọc được sơ đồ đường di chuyển của “Dẫn bóng theo đường vòng, đường zíc-zắc” và dự đoán đúng vị trí tổ mình.</t>
+          <t>Năng lực số 1.1 CB2c: HS đọc được sơ đồ đường di chuyển của “Dẫn bóng thay đổi tốc độ, dẫn bóng theo đường vòng” và dự đoán đúng vị trí tổ mình.</t>
         </is>
       </c>
     </row>
@@ -12167,11 +12140,7 @@
           <t>53</t>
         </is>
       </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS điền và đọc được bảng theo dõi phần kĩ năng vận động cơ bản (leo, trèo) và Bóng rổ (dẫn bóng), tự xác định nội dung cần cố gắng thêm.</t>
-        </is>
-      </c>
+      <c r="H56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -12201,11 +12170,7 @@
           <t>54</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Chuyền và bắt bóng bằng hai tay trước ngực” với động tác mẫu trong clip.</t>
-        </is>
-      </c>
+      <c r="H57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -12235,11 +12200,7 @@
           <t>55</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS điền và đọc được bảng theo dõi phần kĩ năng vận động cơ bản (leo, trèo) và Bóng rổ (dẫn bóng), tự xác định nội dung cần cố gắng thêm.</t>
-        </is>
-      </c>
+      <c r="H58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -12271,7 +12232,8 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Chuyền và bắt bóng bằng hai tay trước ngực” với động tác mẫu trong clip.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài “Chuyền và bắt bóng bằng hai tay trên cao”, GV chiếu trên tivi video kĩ thuật
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lượt chuyền bóng của vài cặp rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi hay gặp như chuyền quá mạnh, tay đón bóng cứng</t>
         </is>
       </c>
     </row>
@@ -12303,12 +12265,7 @@
           <t>57</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài “Chuyền và bắt bóng bằng hai tay trên cao”, GV chiếu trên tivi video kĩ thuật
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lượt chuyền bóng của vài cặp rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi hay gặp như chuyền quá mạnh, tay đón bóng cứng</t>
-        </is>
-      </c>
+      <c r="H60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -12338,11 +12295,7 @@
           <t>58</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Làm quen động tác ném rổ bằng một tay trên vai tại chỗ” với động tác mẫu trong clip.</t>
-        </is>
-      </c>
+      <c r="H61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -12372,11 +12325,7 @@
           <t>59</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 6.1 CB2a: HS đọc được nhận xét của ứng dụng về “Luyện tập hai bước ném rổ và phát triển thể lực” và biết đối chiếu với nhận xét của GV.</t>
-        </is>
-      </c>
+      <c r="H62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -12408,7 +12357,7 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Làm quen động tác ném rổ bằng một tay trên vai tại chỗ” với động tác mẫu trong clip.</t>
+          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Động tác hai bước ném rổ bằng một tay trên vai” với động tác mẫu trong clip.</t>
         </is>
       </c>
     </row>
@@ -12476,7 +12425,7 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS mô tả được đường đi của tay, chân trong “an toàn dưới nước và làm quen với nước” nhờ clip quay dưới mặt nước.</t>
+          <t>Năng lực số 6.1 CB2a: HS đọc được nhận xét của ứng dụng về “Động tác hai bước ném rổ bằng một tay trên vai” và biết đối chiếu với nhận xét của GV.</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12459,7 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở phần Luyện tập, GV quay lượt tập của vài.</t>
+          <t>Năng lực số 1.1 CB2c: HS tra và ghi được 3 điều luật liên quan đến “bóng rổ”, nêu rõ lấy từ nguồn nào.</t>
         </is>
       </c>
     </row>
@@ -12542,11 +12491,7 @@
           <t>64</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Động tác tay bơi trườn sấp” với động tác mẫu trong clip.</t>
-        </is>
-      </c>
+      <c r="H67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -12576,11 +12521,7 @@
           <t>65</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Phối hợp động tác tay với nhịp thở” với động tác mẫu trong clip.</t>
-        </is>
-      </c>
+      <c r="H68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -12640,11 +12581,7 @@
           <t>67</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở phần Luyện tập, GV quay lượt tập của vài.</t>
-        </is>
-      </c>
+      <c r="H70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -12674,11 +12611,7 @@
           <t>68</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS mô tả được đường đi của tay, chân trong “phối hợp bơi trườn sấp và an toàn dưới nước” nhờ clip quay dưới mặt nước.</t>
-        </is>
-      </c>
+      <c r="H71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -26164,11 +26097,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 2): Cho HS xem hiện vật, di tích liên quan “Triều lý và việc định đô ở thăng long” qua bảo tàng số.</t>
-        </is>
-      </c>
+      <c r="H26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -26260,11 +26189,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>NLS-ST (Cơ bản 2): HS dùng công cụ trên máy dựng trục thời gian, sắp các sự kiện của bài theo đúng thứ tự.</t>
-        </is>
-      </c>
+      <c r="H29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -26416,11 +26341,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 2): Cho HS xem hiện vật, di tích liên quan “Khởi nghĩa lam sơn và triều hậu lê” qua bảo tàng số.</t>
-        </is>
-      </c>
+      <c r="H34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -26512,11 +26433,7 @@
           <t>34</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>NLS-ST (Cơ bản 2): HS dùng công cụ trên máy dựng trục thời gian, sắp các sự kiện của bài theo đúng thứ tự.</t>
-        </is>
-      </c>
+      <c r="H37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -27190,11 +27107,7 @@
           <t>55</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 2): Dùng quả địa cầu số hoặc bản đồ thế giới tương tác.</t>
-        </is>
-      </c>
+      <c r="H58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">

--- a/assets/docs/lop5/KHDH ca khoi - Lop 5.xlsx
+++ b/assets/docs/lop5/KHDH ca khoi - Lop 5.xlsx
@@ -15082,7 +15082,7 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.5 CB2a: HS chỉ ra được lời nhắn nào là tôn trọng, lời nhắn nào là trêu chọc, xúc phạm và chọn được cách trả lời phù hợp.
+          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.
 KNS: KN ứng phó với tình huống nguy hiểm và tìm kiếm sự trợ giúp.</t>
         </is>
       </c>
@@ -15117,7 +15117,7 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.
+          <t>Năng lực số 2.5 CB2a: HS chỉ ra được lời nhắn nào là tôn trọng, lời nhắn nào là trêu chọc, xúc phạm và chọn được cách trả lời phù hợp.
 KNS: KN ứng phó với tình huống nguy hiểm và tìm kiếm sự trợ giúp.</t>
         </is>
       </c>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.
+          <t>Năng lực số 1.3 CB2a: HS nhận biết cách ghi lại, sắp xếp số liệu khảo sát môi trường (lượng rác, cây xanh…) một cách đơn giản trên bảng số.
 QPAN: Tổ chức tham quan di tích lịch sử, nhà truyền thống ở địa phương hoặc xem tư liệu thay thế; giáo dục ý thức bảo vệ chủ quyền biển, đảo; trách nhiệm công dân trong xây dựng và bảo vệ Tổ quốc.</t>
         </is>
       </c>

--- a/assets/docs/lop5/KHDH ca khoi - Lop 5.xlsx
+++ b/assets/docs/lop5/KHDH ca khoi - Lop 5.xlsx
@@ -12765,7 +12765,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -12868,7 +12868,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -13005,7 +13005,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -13075,7 +13075,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -13109,7 +13109,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -13179,7 +13179,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -13213,7 +13213,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -13283,7 +13283,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -13486,7 +13486,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -13521,7 +13521,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -13556,7 +13556,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -13591,7 +13591,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -13625,7 +13625,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -13660,7 +13660,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -13695,7 +13695,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -13764,7 +13764,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -13868,7 +13868,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -13903,7 +13903,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
@@ -13967,7 +13967,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
@@ -14003,7 +14003,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -14038,7 +14038,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
@@ -14073,7 +14073,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -14108,7 +14108,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
@@ -14138,7 +14138,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
@@ -14207,7 +14207,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -14241,7 +14241,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
@@ -14311,7 +14311,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
@@ -14376,7 +14376,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -14411,7 +14411,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -14475,7 +14475,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
@@ -14579,7 +14579,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
@@ -14821,7 +14821,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
@@ -14855,7 +14855,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -14890,7 +14890,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
@@ -14955,7 +14955,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
@@ -14990,7 +14990,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -15025,7 +15025,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
@@ -15060,7 +15060,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
@@ -15095,7 +15095,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr"/>
@@ -15130,7 +15130,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
@@ -15165,7 +15165,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr"/>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr"/>
@@ -15338,7 +15338,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
@@ -15373,7 +15373,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr"/>
@@ -15407,7 +15407,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr"/>
@@ -15442,7 +15442,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>
@@ -15472,7 +15472,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr"/>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr"/>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr"/>
@@ -15576,7 +15576,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
@@ -15611,7 +15611,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr"/>
@@ -15715,7 +15715,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
@@ -15750,7 +15750,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
@@ -15820,7 +15820,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr"/>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr"/>
@@ -15920,7 +15920,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr"/>
@@ -15990,7 +15990,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr"/>
@@ -16060,7 +16060,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr"/>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr"/>
@@ -16129,7 +16129,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr"/>
@@ -16164,7 +16164,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr"/>
@@ -16194,7 +16194,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr"/>
@@ -16229,7 +16229,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr"/>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr"/>
@@ -16299,7 +16299,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr"/>
@@ -16333,7 +16333,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr"/>
@@ -23100,7 +23100,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -23164,7 +23164,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -23199,7 +23199,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -23229,7 +23229,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -23255,7 +23255,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -23289,7 +23289,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -23320,7 +23320,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -23354,7 +23354,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -23418,7 +23418,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -23449,7 +23449,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -23479,7 +23479,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -23514,7 +23514,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -23544,7 +23544,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -23579,7 +23579,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -23669,7 +23669,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -23705,7 +23705,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -23735,7 +23735,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -23770,7 +23770,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -23800,7 +23800,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -23835,7 +23835,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -23866,7 +23866,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -23892,7 +23892,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -23922,7 +23922,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -23956,7 +23956,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -23986,7 +23986,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -24021,7 +24021,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -24051,7 +24051,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -24111,7 +24111,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -24205,7 +24205,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
@@ -24240,7 +24240,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -24270,7 +24270,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
@@ -24300,7 +24300,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: VI KHUẨN</t>
+          <t>Chủ đề 4: Vi khuẩn</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -24334,7 +24334,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: VI KHUẨN</t>
+          <t>Chủ đề 4: Vi khuẩn</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
@@ -24364,7 +24364,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: VI KHUẨN</t>
+          <t>Chủ đề 4: Vi khuẩn</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -24399,7 +24399,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: VI KHUẨN</t>
+          <t>Chủ đề 4: Vi khuẩn</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
@@ -24429,7 +24429,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: VI KHUẨN</t>
+          <t>Chủ đề 4: Vi khuẩn</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -24464,7 +24464,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: VI KHUẨN</t>
+          <t>Chủ đề 4: Vi khuẩn</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: VI KHUẨN</t>
+          <t>Chủ đề 4: Vi khuẩn</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
@@ -24524,7 +24524,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -24559,7 +24559,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
@@ -24589,7 +24589,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -24623,7 +24623,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -24653,7 +24653,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -24679,7 +24679,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -24713,7 +24713,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
@@ -24773,7 +24773,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
@@ -24809,7 +24809,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
@@ -24839,7 +24839,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
@@ -24869,7 +24869,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
@@ -24903,7 +24903,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
@@ -24933,7 +24933,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
@@ -24963,7 +24963,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
@@ -24993,7 +24993,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
@@ -25023,7 +25023,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -25058,7 +25058,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
@@ -25088,7 +25088,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
@@ -25114,7 +25114,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
@@ -25149,7 +25149,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -25179,7 +25179,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
@@ -25205,7 +25205,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
@@ -27703,13 +27703,13 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>STARTER</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>STARTER</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -27743,13 +27743,13 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>STARTER</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>STARTER</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -27782,13 +27782,13 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>STARTER</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>STARTER</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -27821,13 +27821,13 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>UNIT 1</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>UNIT 1</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -27860,13 +27860,13 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>UNIT 1</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>UNIT 1</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -27898,13 +27898,13 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>UNIT 1</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>UNIT 1</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -27938,13 +27938,13 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>UNIT 1</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>UNIT 1</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -27976,13 +27976,13 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>UNIT 1</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>UNIT 1</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -28016,13 +28016,13 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>UNIT 1</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>UNIT 1</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -28054,13 +28054,13 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>UNIT 2</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>UNIT 2</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -28094,13 +28094,13 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>UNIT 2</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>UNIT 2</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -28132,13 +28132,13 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>UNIT 2</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>UNIT 2</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -28172,13 +28172,13 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>UNIT 2</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>UNIT 2</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -28210,13 +28210,13 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>UNIT 2</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>UNIT 2</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -28250,13 +28250,13 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>UNIT 2</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>UNIT 2</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -28288,13 +28288,13 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>UNIT 3</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>UNIT 3</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -28328,13 +28328,13 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>UNIT 3</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>UNIT 3</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -28366,13 +28366,13 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>UNIT 3</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>UNIT 3</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -28406,13 +28406,13 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>UNIT 3</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>UNIT 3</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -28444,13 +28444,13 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>UNIT 3</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>UNIT 3</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -28484,13 +28484,13 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>UNIT 3</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>UNIT 3</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -28522,13 +28522,13 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>UNIT 4</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>UNIT 4</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -28562,13 +28562,13 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>UNIT 4</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>UNIT 4</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -28600,13 +28600,13 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>UNIT 4</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>UNIT 4</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -28640,13 +28640,13 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>UNIT 4</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>UNIT 4</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -28680,13 +28680,13 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>UNIT 4</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>UNIT 4</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -28720,13 +28720,13 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>UNIT 4</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>UNIT 4</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -28758,13 +28758,13 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>UNIT 5</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>UNIT 5</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -28798,13 +28798,13 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>UNIT 5</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>UNIT 5</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -28836,13 +28836,13 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>UNIT 5</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>UNIT 5</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -28876,13 +28876,13 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>UNIT 5</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>UNIT 5</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -28914,13 +28914,13 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>UNIT 5</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>UNIT 5</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -28954,13 +28954,13 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>UNIT 5</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>UNIT 5</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -28994,13 +28994,13 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 1</t>
+          <t>Review 1</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 1</t>
+          <t>Review 1</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -29028,13 +29028,13 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 1</t>
+          <t>Review 1</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 1</t>
+          <t>Review 1</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -29067,13 +29067,13 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 1</t>
+          <t>Review 1</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 1</t>
+          <t>Review 1</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -29106,13 +29106,13 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>UNIT 6</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>UNIT 6</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -29146,13 +29146,13 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>UNIT 6</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>UNIT 6</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -29184,13 +29184,13 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>UNIT 6</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>UNIT 6</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -29224,13 +29224,13 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>UNIT 6</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>UNIT 6</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -29262,13 +29262,13 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>UNIT 6</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>UNIT 6</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -29302,13 +29302,13 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>UNIT 6</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>UNIT 6</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -29340,13 +29340,13 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>UNIT 7</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>UNIT 7</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -29380,13 +29380,13 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>UNIT 7</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>UNIT 7</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -29418,13 +29418,13 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>UNIT 7</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>UNIT 7</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -29458,13 +29458,13 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>UNIT 7</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>UNIT 7</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -29496,13 +29496,13 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>UNIT 7</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>UNIT 7</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -29536,13 +29536,13 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>UNIT 7</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>UNIT 7</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -29574,13 +29574,13 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>UNIT 8</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>UNIT 8</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -29614,13 +29614,13 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>UNIT 8</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>UNIT 8</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -29652,13 +29652,13 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>UNIT 8</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>UNIT 8</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -29692,13 +29692,13 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>UNIT 8</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>UNIT 8</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -29730,13 +29730,13 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>UNIT 8</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>UNIT 8</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -29770,13 +29770,13 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>UNIT 8</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>UNIT 8</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -29808,13 +29808,13 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>UNIT 9</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>UNIT 9</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -29848,13 +29848,13 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>UNIT 9</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>UNIT 9</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -29886,13 +29886,13 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>UNIT 9</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>UNIT 9</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -29926,13 +29926,13 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>UNIT 9</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>UNIT 9</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -29964,13 +29964,13 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>UNIT 9</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>UNIT 9</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -30004,13 +30004,13 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>UNIT 9</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>UNIT 9</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -30042,13 +30042,13 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>UNIT 10</t>
+          <t>Unit 10</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>UNIT 10</t>
+          <t>Unit 10</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -30082,13 +30082,13 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>UNIT 10</t>
+          <t>Unit 10</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>UNIT 10</t>
+          <t>Unit 10</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -30120,13 +30120,13 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>UNIT 10</t>
+          <t>Unit 10</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>UNIT 10</t>
+          <t>Unit 10</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -30160,13 +30160,13 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>UNIT 10</t>
+          <t>Unit 10</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>UNIT 10</t>
+          <t>Unit 10</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -30198,13 +30198,13 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>UNIT 10</t>
+          <t>Unit 10</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>UNIT 10</t>
+          <t>Unit 10</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -30238,13 +30238,13 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>UNIT 10</t>
+          <t>Unit 10</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>UNIT 10</t>
+          <t>Unit 10</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -30278,13 +30278,13 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 2</t>
+          <t>Review 2</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 2</t>
+          <t>Review 2</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -30312,13 +30312,13 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 2</t>
+          <t>Review 2</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr"/>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 2</t>
+          <t>Review 2</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -30351,13 +30351,13 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 2</t>
+          <t>Review 2</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 2</t>
+          <t>Review 2</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -30463,13 +30463,13 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>UNIT 11</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>UNIT 11</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -30503,13 +30503,13 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>UNIT 11</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>UNIT 11</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -30541,13 +30541,13 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>UNIT 11</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr"/>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>UNIT 11</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -30581,13 +30581,13 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>UNIT 11</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>UNIT 11</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -30619,13 +30619,13 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>UNIT 11</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr"/>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>UNIT 11</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -30659,13 +30659,13 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>UNIT 11</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr"/>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>UNIT 11</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -30697,13 +30697,13 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>UNIT 12</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>UNIT 12</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -30737,13 +30737,13 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>UNIT 12</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr"/>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>UNIT 12</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -30775,13 +30775,13 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>UNIT 12</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr"/>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>UNIT 12</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
@@ -30815,13 +30815,13 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>UNIT 12</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr"/>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>UNIT 12</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -30853,13 +30853,13 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>UNIT 12</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>UNIT 12</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
@@ -30893,13 +30893,13 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>UNIT 12</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr"/>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>UNIT 12</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -30931,13 +30931,13 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>UNIT 13</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>UNIT 13</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -30971,13 +30971,13 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>UNIT 13</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr"/>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>UNIT 13</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -31009,13 +31009,13 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>UNIT 13</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>UNIT 13</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -31049,13 +31049,13 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>UNIT 13</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>UNIT 13</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -31087,13 +31087,13 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>UNIT 13</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>UNIT 13</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
@@ -31127,13 +31127,13 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>UNIT 13</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr"/>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>UNIT 13</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -31165,13 +31165,13 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>UNIT 14</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr"/>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>UNIT 14</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -31205,13 +31205,13 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>UNIT 14</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr"/>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>UNIT 14</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -31243,13 +31243,13 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>UNIT 14</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>UNIT 14</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -31283,13 +31283,13 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>UNIT 14</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr"/>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>UNIT 14</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -31321,13 +31321,13 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>UNIT 14</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>UNIT 14</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -31361,13 +31361,13 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>UNIT 14</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr"/>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>UNIT 14</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -31399,13 +31399,13 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>UNIT 15</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr"/>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>UNIT 15</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -31439,13 +31439,13 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>UNIT 15</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr"/>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>UNIT 15</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -31477,13 +31477,13 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>UNIT 15</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr"/>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>UNIT 15</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -31517,13 +31517,13 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>UNIT 15</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr"/>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>UNIT 15</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -31555,13 +31555,13 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>UNIT 15</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr"/>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>UNIT 15</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -31595,13 +31595,13 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>UNIT 15</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr"/>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>UNIT 15</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -31633,13 +31633,13 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 3</t>
+          <t>Review 3</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr"/>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 3</t>
+          <t>Review 3</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -31672,13 +31672,13 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 3</t>
+          <t>Review 3</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr"/>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 3</t>
+          <t>Review 3</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -31711,13 +31711,13 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 3</t>
+          <t>Review 3</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr"/>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 3</t>
+          <t>Review 3</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -31745,13 +31745,13 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>UNIT 16</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr"/>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>UNIT 16</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -31785,13 +31785,13 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>UNIT 16</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr"/>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>UNIT 16</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -31823,13 +31823,13 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>UNIT 16</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr"/>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>UNIT 16</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -31863,13 +31863,13 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>UNIT 16</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr"/>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>UNIT 16</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -31901,13 +31901,13 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>UNIT 16</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr"/>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>UNIT 16</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -31941,13 +31941,13 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>UNIT 16</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr"/>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>UNIT 16</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -31979,13 +31979,13 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>UNIT 17</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr"/>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>UNIT 17</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -32019,13 +32019,13 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>UNIT 17</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr"/>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>UNIT 17</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
@@ -32057,13 +32057,13 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>UNIT 17</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr"/>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>UNIT 17</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -32097,13 +32097,13 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>UNIT 17</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr"/>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>UNIT 17</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -32135,13 +32135,13 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>UNIT 17</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr"/>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>UNIT 17</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -32175,13 +32175,13 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>UNIT 17</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr"/>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>UNIT 17</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
@@ -32213,13 +32213,13 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>UNIT 18</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr"/>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>UNIT 18</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -32253,13 +32253,13 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>UNIT 18</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr"/>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>UNIT 18</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -32291,13 +32291,13 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>UNIT 18</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr"/>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>UNIT 18</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -32331,13 +32331,13 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>UNIT 18</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr"/>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>UNIT 18</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
@@ -32371,13 +32371,13 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>UNIT 18</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr"/>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>UNIT 18</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -32410,13 +32410,13 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>UNIT 18</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr"/>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>UNIT 18</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -32448,13 +32448,13 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>UNIT 19</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr"/>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>UNIT 19</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -32488,13 +32488,13 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>UNIT 19</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr"/>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>UNIT 19</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -32526,13 +32526,13 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>UNIT 19</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr"/>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>UNIT 19</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -32566,13 +32566,13 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>UNIT 19</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr"/>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>UNIT 19</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -32604,13 +32604,13 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>UNIT 19</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr"/>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>UNIT 19</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -32644,13 +32644,13 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>UNIT 19</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr"/>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>UNIT 19</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
@@ -32682,13 +32682,13 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>UNIT 20</t>
+          <t>Unit 20</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr"/>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>UNIT 20</t>
+          <t>Unit 20</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -32722,13 +32722,13 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>UNIT 20</t>
+          <t>Unit 20</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr"/>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>UNIT 20</t>
+          <t>Unit 20</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -32760,13 +32760,13 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>UNIT 20</t>
+          <t>Unit 20</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr"/>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>UNIT 20</t>
+          <t>Unit 20</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -32800,13 +32800,13 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>UNIT 20</t>
+          <t>Unit 20</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr"/>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>UNIT 20</t>
+          <t>Unit 20</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
@@ -32838,13 +32838,13 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>UNIT 20</t>
+          <t>Unit 20</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr"/>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>UNIT 20</t>
+          <t>Unit 20</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -32878,13 +32878,13 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>UNIT 20</t>
+          <t>Unit 20</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr"/>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>UNIT 20</t>
+          <t>Unit 20</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
@@ -32916,13 +32916,13 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 4</t>
+          <t>Review 4</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr"/>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 4</t>
+          <t>Review 4</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -32955,13 +32955,13 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 4</t>
+          <t>Review 4</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr"/>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 4</t>
+          <t>Review 4</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
@@ -32994,13 +32994,13 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 4</t>
+          <t>Review 4</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr"/>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>REVIEW 4</t>
+          <t>Review 4</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -35535,7 +35535,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: KHÚC CA NGÀY MỚI</t>
+          <t>Chủ đề 1: Khúc ca ngày mới</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -35569,7 +35569,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: KHÚC CA NGÀY MỚI</t>
+          <t>Chủ đề 1: Khúc ca ngày mới</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -35603,7 +35603,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: KHÚC CA NGÀY MỚI</t>
+          <t>Chủ đề 1: Khúc ca ngày mới</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -35638,7 +35638,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: KHÚC CA NGÀY MỚI</t>
+          <t>Chủ đề 1: Khúc ca ngày mới</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -35674,7 +35674,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: GIAI ĐIỆU QUÊ HƯƠNG</t>
+          <t>Chủ đề 2: Giai điệu quê hương</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -35709,7 +35709,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: GIAI ĐIỆU QUÊ HƯƠNG</t>
+          <t>Chủ đề 2: Giai điệu quê hương</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -35743,7 +35743,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: GIAI ĐIỆU QUÊ HƯƠNG</t>
+          <t>Chủ đề 2: Giai điệu quê hương</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -35777,7 +35777,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: GIAI ĐIỆU QUÊ HƯƠNG</t>
+          <t>Chủ đề 2: Giai điệu quê hương</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -35813,7 +35813,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: BAY VÀO TƯƠNG LAI</t>
+          <t>Chủ đề 3: Bay vào tương lai</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -35847,7 +35847,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: BAY VÀO TƯƠNG LAI</t>
+          <t>Chủ đề 3: Bay vào tương lai</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -35881,7 +35881,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: BAY VÀO TƯƠNG LAI</t>
+          <t>Chủ đề 3: Bay vào tương lai</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -35915,7 +35915,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: BAY VÀO TƯƠNG LAI</t>
+          <t>Chủ đề 3: Bay vào tương lai</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -35951,7 +35951,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: CHÀO MÙA XUÂN ĐẾN</t>
+          <t>Chủ đề 4: Chào mùa xuân đến</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -35985,7 +35985,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: CHÀO MÙA XUÂN ĐẾN</t>
+          <t>Chủ đề 4: Chào mùa xuân đến</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -36019,7 +36019,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: CHÀO MÙA XUÂN ĐẾN</t>
+          <t>Chủ đề 4: Chào mùa xuân đến</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -36053,7 +36053,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: CHÀO MÙA XUÂN ĐẾN</t>
+          <t>Chủ đề 4: Chào mùa xuân đến</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -36153,7 +36153,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: THIÊN NHIÊN TƯƠI ĐẸP</t>
+          <t>Chủ đề 5: Thiên nhiên tươi đẹp</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -36187,7 +36187,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: THIÊN NHIÊN TƯƠI ĐẸP</t>
+          <t>Chủ đề 5: Thiên nhiên tươi đẹp</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -36221,7 +36221,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: THIÊN NHIÊN TƯƠI ĐẸP</t>
+          <t>Chủ đề 5: Thiên nhiên tươi đẹp</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -36256,7 +36256,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: THIÊN NHIÊN TƯƠI ĐẸP</t>
+          <t>Chủ đề 5: Thiên nhiên tươi đẹp</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -36292,7 +36292,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: ƯỚC MƠ TUỔI THƠ</t>
+          <t>Chủ đề 6: Ước mơ tuổi thơ</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -36326,7 +36326,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: ƯỚC MƠ TUỔI THƠ</t>
+          <t>Chủ đề 6: Ước mơ tuổi thơ</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -36360,7 +36360,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: ƯỚC MƠ TUỔI THƠ</t>
+          <t>Chủ đề 6: Ước mơ tuổi thơ</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -36394,7 +36394,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: ƯỚC MƠ TUỔI THƠ</t>
+          <t>Chủ đề 6: Ước mơ tuổi thơ</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -36430,7 +36430,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: ÂM NHẠC NƯỚC NGOÀI</t>
+          <t>Chủ đề 7: Âm nhạc nước ngoài</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -36464,7 +36464,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: ÂM NHẠC NƯỚC NGOÀI</t>
+          <t>Chủ đề 7: Âm nhạc nước ngoài</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -36499,7 +36499,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: ÂM NHẠC NƯỚC NGOÀI</t>
+          <t>Chủ đề 7: Âm nhạc nước ngoài</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -36534,7 +36534,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: ÂM NHẠC NƯỚC NGOÀI</t>
+          <t>Chủ đề 7: Âm nhạc nước ngoài</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -36570,7 +36570,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 8: KHÚC CA HÈ VỀ</t>
+          <t>Chủ đề 8: Khúc ca hè về</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -36604,7 +36604,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 8: KHÚC CA HÈ VỀ</t>
+          <t>Chủ đề 8: Khúc ca hè về</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -36638,7 +36638,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 8: KHÚC CA HÈ VỀ</t>
+          <t>Chủ đề 8: Khúc ca hè về</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
